--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33222-2026 artfynd.xlsx
+++ b/artfynd/A 33222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137163108</v>
       </c>
       <c r="B2" t="n">
-        <v>97707</v>
+        <v>97711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
